--- a/mosip_master/xlsx/loc_hierarchy_list.xlsx
+++ b/mosip_master/xlsx/loc_hierarchy_list.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6800" tabRatio="500"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -72,7 +72,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;\ * #,##0_ ;_ &quot;₹&quot;\ * \-#,##0_ ;_ &quot;₹&quot;\ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -83,12 +83,6 @@
       <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
@@ -572,18 +566,21 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -592,122 +589,119 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -716,12 +710,11 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1255,13 +1248,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultColWidth="8.42727272727273" defaultRowHeight="14.5" outlineLevelCol="3"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="8.42857142857143" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="18.4272727272727" customWidth="1"/>
-    <col min="2" max="2" width="21.2818181818182" customWidth="1"/>
-    <col min="3" max="3" width="24.1454545454545" customWidth="1"/>
-    <col min="4" max="4" width="25.4181818181818" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="21.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="24.1428571428571" customWidth="1"/>
+    <col min="4" max="4" width="25.4190476190476" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1348,73 +1341,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D19" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D6" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>

--- a/mosip_master/xlsx/loc_hierarchy_list.xlsx
+++ b/mosip_master/xlsx/loc_hierarchy_list.xlsx
@@ -1253,7 +1253,7 @@
   <cols>
     <col min="1" max="1" width="18.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="21.2857142857143" customWidth="1"/>
-    <col min="3" max="3" width="24.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="25.4190476190476" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1275,11 +1275,11 @@
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="5">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0</v>
       </c>
       <c r="D2" s="6" t="b">
         <v>1</v>
@@ -1289,11 +1289,11 @@
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>6</v>
-      </c>
-      <c r="C3" s="5">
-        <v>1</v>
       </c>
       <c r="D3" s="6" t="b">
         <v>1</v>
@@ -1303,11 +1303,11 @@
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="5">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>7</v>
-      </c>
-      <c r="C4" s="5">
-        <v>2</v>
       </c>
       <c r="D4" s="6" t="b">
         <v>1</v>
@@ -1317,11 +1317,11 @@
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="C5" s="5">
-        <v>3</v>
       </c>
       <c r="D5" s="6" t="b">
         <v>1</v>
@@ -1331,11 +1331,11 @@
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="5">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="C6" s="5">
-        <v>4</v>
       </c>
       <c r="D6" s="6" t="b">
         <v>1</v>
